--- a/premise/data/additional_inventories/lci-synfuels-from-FT-from-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-synfuels-from-FT-from-electrolysis.xlsx
@@ -5741,8 +5741,12 @@
       <c r="A270" t="s">
         <v>9</v>
       </c>
-      <c r="B270" t="s">
-        <v>50</v>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>APPROVED GTL-PLANT STEEL-GRADE SOURCE CORRECTION, 2026-10-18. Van der Giesen, Kleijn and Kramer (2014), Energy and Climate Impacts of Producing Synthetic Hydrocarbon Fuels from CO2, Environmental Science &amp; Technology 48, 7111-7121, DOI 10.1021/es500191g; supporting information https://doi.org/10.1021/es500191g.s001, Table S21, page S25. The source specifies 7.20E+06 kg low-alloy steel plus 7.20E+06 kg reinforcing steel per GTL plant. Its plant-construction narrative also explicitly describes an equal division of reinforcing and low-alloy steel. Replace the transcribed stainless/chromium-steel 18/8 purchase with the existing market for steel, low-alloyed, while retaining the 7,200,000 kg amount and inherited GLO market geography. This is a source material-identity correction, not validation of the exact alloy grade, a modern plant design, manufacturing yields or future engineering. The original source uses RER supply; supply geography is not revised in this targeted change. Reinforcing steel, concrete, 14,400,000 kg waste bulk iron, concrete disposal, land occupation, plant output, every fuel-plant dose and lifetime allocation remain unchanged. No extra equipment, treatment, metal-content factor, recovered-metal credit or primary/secondary split is introduced. This restores the historical source recipe; full system metal effects, plant lifetime arithmetic, RWGS equipment and catalyst coverage remain separate and unvalidated by this correction.
+PREVIOUS SOURCE NOTES:
+Represents an input of 1.120.000 m2 of land, 14.400 ton of steel in an assumed equal division of reinforcing and low alloyed steel, 345.000 m3 of concrete.</t>
+        </is>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.2">
@@ -5822,8 +5826,10 @@
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A276" t="s">
-        <v>28</v>
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
       </c>
       <c r="B276" s="3">
         <v>7200000</v>
@@ -5837,8 +5843,10 @@
       <c r="F276" t="s">
         <v>17</v>
       </c>
-      <c r="G276" t="s">
-        <v>29</v>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-synfuels-from-FT-from-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-synfuels-from-FT-from-electrolysis.xlsx
@@ -6266,8 +6266,13 @@
       <c r="A314" t="s">
         <v>9</v>
       </c>
-      <c r="B314" t="s">
-        <v>73</v>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>APPROVED RWGS TWO-VESSEL STEEL SOURCE CORRECTION, 2026-10-18. Van der Giesen, Kleijn and Kramer (2014), Energy and Climate Impacts of Producing Synthetic Hydrocarbon Fuels from CO2, Environmental Science &amp; Technology 48, 7111-7121, DOI 10.1021/es500191g; supporting information https://doi.org/10.1021/es500191g.s001, Table S18, page S24, and reactor narrative on page S7. Each vessel contains 4,760 kg steel, split equally between low-alloy and chromium steel. One declared reactor-construction unit represents TWO parallel vessels: 2 vessels * 4,760 kg/vessel * 0.5 = 4,760 kg of EACH steel grade. The previous 2,380 kg purchases each represented only one vessel, despite the existing two-vessel catalyst, sorbent and waste quantities. Restore both steel purchases to 4,760 kg, totaling 9,520 kg and matching the existing -9,520 kg steel-treatment input. Keep every supplier identity, processing form and geography, the one-unit output, 26,700 kg lifetime zeolite, 6,600 kg lifetime catalyst, and all other equipment and process coefficients unchanged. Preserve the inherited 1.93E-09 construction units/kg CO allocation: its separate disputed source throughput/lifetime arithmetic is not corrected here. This restores the historical source two-vessel boundary, not independent validation of modern engineering, material retention or manufacturing and treatment yields. No primary/secondary split, new metal-content factor, recovery credit, extra equipment or invented catalyst dose is introduced. Separate tank/catalyst coverage and full system metal effects remain unvalidated by this correction.
+PREVIOUS SOURCE NOTES:
+The reactor vessel consists of 4760 kg of steel (assuming 50% low alloyed steel and 50% chromium steel) and is filled with a mixture of 440 kg of RWGS catalyst and 1780 kg of sorbent, which need to be renewed every 4 years.14 Over a reactor lifetime of 30 years therefore 30/4 x 440 kg = 3300 kg of catalyst and 30/4 x 1780 kg = 13350 kg of sorbent is needed. Since two identical reactors are use in parallel all numbers are doubled in the unit process representing the construction of the fixed bed
+reactor.</t>
+        </is>
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.2">
@@ -6334,8 +6339,8 @@
         <v>74</v>
       </c>
       <c r="B319" s="3">
-        <f>4760/2</f>
-        <v>2380</v>
+        <f>2*4760/2</f>
+        <v>4760</v>
       </c>
       <c r="C319" t="s">
         <v>27</v>
@@ -6349,8 +6354,12 @@
       <c r="G319" t="s">
         <v>75</v>
       </c>
-      <c r="H319" t="s">
-        <v>119</v>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>APPROVED RWGS TWO-VESSEL STEEL SOURCE CORRECTION, 2026-10-18. Van der Giesen, Kleijn and Kramer (2014), Energy and Climate Impacts of Producing Synthetic Hydrocarbon Fuels from CO2, Environmental Science &amp; Technology 48, 7111-7121, DOI 10.1021/es500191g; supporting information https://doi.org/10.1021/es500191g.s001, Table S18, page S24, and reactor narrative on page S7. Each vessel contains 4,760 kg steel, split equally between low-alloy and chromium steel. One declared reactor-construction unit represents TWO parallel vessels: 2 vessels * 4,760 kg/vessel * 0.5 = 4,760 kg of EACH steel grade. The previous 2,380 kg purchases each represented only one vessel, despite the existing two-vessel catalyst, sorbent and waste quantities. Restore both steel purchases to 4,760 kg, totaling 9,520 kg and matching the existing -9,520 kg steel-treatment input. Keep every supplier identity, processing form and geography, the one-unit output, 26,700 kg lifetime zeolite, 6,600 kg lifetime catalyst, and all other equipment and process coefficients unchanged. Preserve the inherited 1.93E-09 construction units/kg CO allocation: its separate disputed source throughput/lifetime arithmetic is not corrected here. This restores the historical source two-vessel boundary, not independent validation of modern engineering, material retention or manufacturing and treatment yields. No primary/secondary split, new metal-content factor, recovery credit, extra equipment or invented catalyst dose is introduced. Separate tank/catalyst coverage and full system metal effects remain unvalidated by this correction.
+PREVIOUS SOURCE NOTES:
+The reactor vessel consists of 4760 kg of steel (assuming 50% low alloyed steel and 50% chromium steel) </t>
+        </is>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.2">
@@ -6378,8 +6387,8 @@
         <v>76</v>
       </c>
       <c r="B321" s="3">
-        <f>4760/2</f>
-        <v>2380</v>
+        <f>2*4760/2</f>
+        <v>4760</v>
       </c>
       <c r="C321" t="s">
         <v>27</v>
@@ -6393,8 +6402,12 @@
       <c r="G321" t="s">
         <v>77</v>
       </c>
-      <c r="H321" t="s">
-        <v>119</v>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>APPROVED RWGS TWO-VESSEL STEEL SOURCE CORRECTION, 2026-10-18. Van der Giesen, Kleijn and Kramer (2014), Energy and Climate Impacts of Producing Synthetic Hydrocarbon Fuels from CO2, Environmental Science &amp; Technology 48, 7111-7121, DOI 10.1021/es500191g; supporting information https://doi.org/10.1021/es500191g.s001, Table S18, page S24, and reactor narrative on page S7. Each vessel contains 4,760 kg steel, split equally between low-alloy and chromium steel. One declared reactor-construction unit represents TWO parallel vessels: 2 vessels * 4,760 kg/vessel * 0.5 = 4,760 kg of EACH steel grade. The previous 2,380 kg purchases each represented only one vessel, despite the existing two-vessel catalyst, sorbent and waste quantities. Restore both steel purchases to 4,760 kg, totaling 9,520 kg and matching the existing -9,520 kg steel-treatment input. Keep every supplier identity, processing form and geography, the one-unit output, 26,700 kg lifetime zeolite, 6,600 kg lifetime catalyst, and all other equipment and process coefficients unchanged. Preserve the inherited 1.93E-09 construction units/kg CO allocation: its separate disputed source throughput/lifetime arithmetic is not corrected here. This restores the historical source two-vessel boundary, not independent validation of modern engineering, material retention or manufacturing and treatment yields. No primary/secondary split, new metal-content factor, recovery credit, extra equipment or invented catalyst dose is introduced. Separate tank/catalyst coverage and full system metal effects remain unvalidated by this correction.
+PREVIOUS SOURCE NOTES:
+The reactor vessel consists of 4760 kg of steel (assuming 50% low alloyed steel and 50% chromium steel) </t>
+        </is>
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-synfuels-from-FT-from-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-synfuels-from-FT-from-electrolysis.xlsx
@@ -3372,8 +3372,12 @@
       <c r="A97" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B97" s="9" t="s">
-        <v>40</v>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 45 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Economic allocation between 3 other co-products. Allocation key for this co-product: 6%.</t>
+        </is>
       </c>
     </row>
     <row r="98" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -3514,7 +3518,7 @@
         <v>37</v>
       </c>
       <c r="B105" s="10">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C105" s="9" t="s">
         <v>27</v>
@@ -3629,8 +3633,12 @@
       <c r="A115" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B115" s="9" t="s">
-        <v>42</v>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 44.5 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Economic allocation between 3 other co-products. Allocation key for this co-product: 7%.</t>
+        </is>
       </c>
     </row>
     <row r="116" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -3768,7 +3776,7 @@
         <v>37</v>
       </c>
       <c r="B123" s="10">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C123" s="9" t="s">
         <v>27</v>
@@ -3883,8 +3891,12 @@
       <c r="A133" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B133" s="9" t="s">
-        <v>43</v>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 43.3 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Economic allocation between 3 other co-products. Allocation key for this co-product: 16%.</t>
+        </is>
       </c>
     </row>
     <row r="134" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4025,7 +4037,7 @@
         <v>37</v>
       </c>
       <c r="B141" s="10">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C141" s="9" t="s">
         <v>27</v>
@@ -4140,8 +4152,12 @@
       <c r="A151" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B151" s="9" t="s">
-        <v>44</v>
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 40.2 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 21%.</t>
+        </is>
       </c>
     </row>
     <row r="152" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4282,7 +4298,7 @@
         <v>37</v>
       </c>
       <c r="B159" s="10">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C159" s="9" t="s">
         <v>27</v>
@@ -4399,8 +4415,12 @@
       <c r="A169" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B169" s="9" t="s">
-        <v>45</v>
+      <c r="B169" s="9" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 45 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 18%.</t>
+        </is>
       </c>
     </row>
     <row r="170" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4541,7 +4561,7 @@
         <v>37</v>
       </c>
       <c r="B177" s="10">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C177" s="9" t="s">
         <v>27</v>
@@ -4656,8 +4676,12 @@
       <c r="A187" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B187" s="9" t="s">
-        <v>46</v>
+      <c r="B187" s="9" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 44.5 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 24%.</t>
+        </is>
       </c>
     </row>
     <row r="188" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4795,7 +4819,7 @@
         <v>37</v>
       </c>
       <c r="B195" s="10">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C195" s="9" t="s">
         <v>27</v>
@@ -4910,8 +4934,12 @@
       <c r="A205" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B205" s="9" t="s">
-        <v>47</v>
+      <c r="B205" s="9" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 43.3 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 37%. Post corrected to preserve carbon balance.</t>
+        </is>
       </c>
     </row>
     <row r="206" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -5052,7 +5080,7 @@
         <v>37</v>
       </c>
       <c r="B213" s="10">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C213" s="9" t="s">
         <v>27</v>
@@ -5167,8 +5195,12 @@
       <c r="A223" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B223" s="9" t="s">
-        <v>161</v>
+      <c r="B223" s="9" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from A.E.M. van den Oever, D. Costa, M. Messagie, Prospective life cycle assessment of alternatively fueled heavy-duty trucks, Applied Energy, 2023, https://doi.org/10.1016/j.apenergy.2023.120834. Energy-based allocation between 3 other co-products (diesel, wax and C5-C10 olefins). Allocation key for this co-product: 11%. Post corrected to preserve carbon balance.</t>
+        </is>
       </c>
     </row>
     <row r="224" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -5296,7 +5328,7 @@
         <v>37</v>
       </c>
       <c r="B231" s="10">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C231" s="9" t="s">
         <v>27</v>

--- a/premise/data/additional_inventories/lci-synfuels-from-FT-from-electrolysis.xlsx
+++ b/premise/data/additional_inventories/lci-synfuels-from-FT-from-electrolysis.xlsx
@@ -5606,8 +5606,12 @@
       <c r="A256" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B256" s="9" t="s">
-        <v>30</v>
+      <c r="B256" s="9" t="inlineStr">
+        <is>
+          <t>APPROVED RWGS PAIR-LEVEL THROUGHPUT ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, pages S7-S8 and Table S19, states 2900 kg CO per 30 minutes, 8000 operating hours/year and 30 years, for construction represented by a two-reactor unit. EXPLICIT USER-APPROVED BOUNDARY ASSUMPTION: treat 2900 kg per 30 minutes as total output of the COMPLETE TWO-REACTOR UNIT, not per vessel. Then 1/(2900*2*8000*30) = 7.183908045977011E-10 pair units/kg CO, replacing the inconsistent 1.93E-9. The source duty/parallel-vessel interpretation remains ambiguous: if both vessels each deliver this throughput, the dose would be half this value. This reference accounting assumption is not proof of industrial performance. Keep the corrected two-vessel steel recipe, catalyst/zeolite lifetime quantities, CO output and other material/energy flows unchanged. Historical dose statements are superseded only for this coefficient. No new recovery credit or primary/secondary split.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. Density of syngas: 0.470kg/m3 @1 bar. LHV: 23.9 MJ/kg.</t>
+        </is>
       </c>
     </row>
     <row r="257" spans="1:7" s="9" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -5703,7 +5707,7 @@
         <v>48</v>
       </c>
       <c r="B262" s="10">
-        <v>1.9300000000000002E-9</v>
+        <v>7.183908045977011e-10</v>
       </c>
       <c r="C262" s="9" t="s">
         <v>8</v>
